--- a/media/Levels/kakeraMapLevel11.xlsx
+++ b/media/Levels/kakeraMapLevel11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22204898-B4DB-445A-834A-F1692F2DF37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F1ED7A-2EB1-43FB-9EB8-69D8771F2291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="576" yWindow="72" windowWidth="15660" windowHeight="12168" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -39800,28 +39800,28 @@
         <v>0</v>
       </c>
       <c r="BS87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA87">
         <v>0</v>
@@ -40255,28 +40255,28 @@
         <v>0</v>
       </c>
       <c r="BS88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA88">
         <v>0</v>
@@ -40710,28 +40710,28 @@
         <v>0</v>
       </c>
       <c r="BS89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA89">
         <v>0</v>
@@ -41165,28 +41165,28 @@
         <v>0</v>
       </c>
       <c r="BS90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA90">
         <v>0</v>
@@ -41620,28 +41620,28 @@
         <v>0</v>
       </c>
       <c r="BS91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA91">
         <v>0</v>
@@ -42075,28 +42075,28 @@
         <v>0</v>
       </c>
       <c r="BS92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA92">
         <v>0</v>
@@ -42530,28 +42530,28 @@
         <v>0</v>
       </c>
       <c r="BS93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA93">
         <v>0</v>
@@ -42985,28 +42985,28 @@
         <v>0</v>
       </c>
       <c r="BS94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA94">
         <v>0</v>
@@ -43440,28 +43440,28 @@
         <v>0</v>
       </c>
       <c r="BS95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA95">
         <v>0</v>
